--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -1,43 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D82356-8247-4779-89F3-7151EAAC8C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_in_tray" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="batch_in_tray" sheetId="1" r:id="rId1"/>
+    <sheet name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="tray_type_options">validation_meta!$A$1:$A$13</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>tray_type</t>
+  </si>
+  <si>
+    <t>2 mL反应试管托盘(201000726) [1-24]</t>
+  </si>
+  <si>
+    <t>2 mL试管磁子托盘(201000711) [1-24]</t>
+  </si>
+  <si>
+    <t>反应密封盖托盘(201000712) [1-1]</t>
+  </si>
+  <si>
+    <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
+  </si>
+  <si>
+    <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
+  </si>
+  <si>
+    <t>50 μL Tip 头托盘(201000815) [1-96]</t>
+  </si>
+  <si>
+    <t>1 mL Tip 头托盘(201000731) [1-96]</t>
+  </si>
+  <si>
+    <t>5 mL Tip 头托盘(201000512) [1-24]</t>
+  </si>
+  <si>
+    <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
+  </si>
+  <si>
+    <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
+  </si>
+  <si>
+    <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
+  </si>
+  <si>
+    <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
+  </si>
+  <si>
+    <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
+  </si>
+  <si>
+    <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TB-2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,80 +120,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -417,216 +422,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="55.7265625" customWidth="1" min="3" max="3"/>
-    <col width="6.1796875" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>position</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tray_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>shelf_position</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>storage(格式: 物质|位置; 多个用;隔开)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TB-2-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>8 mL试剂瓶托盘(201000502)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A1|乙醇|3mL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>乙醇|未知</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TB-2-2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2 mL反应试管托盘(201000726)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2mL反应管|耗材库</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation sqref="A2:A101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B101" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" showInputMessage="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>tray_type_options</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="99" verticalDpi="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>2 mL反应试管托盘(201000726) [1-24]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2 mL试管磁子托盘(201000711) [1-24]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>反应密封盖托盘(201000712) [1-1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>50 μL Tip 头托盘(201000815) [1-96]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1 mL Tip 头托盘(201000731) [1-96]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5 mL Tip 头托盘(201000512) [1-24]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -1,107 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D82356-8247-4779-89F3-7151EAAC8C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="batch_in_tray" sheetId="1" r:id="rId1"/>
-    <sheet name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_in_tray" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="tray_type_options">validation_meta!$A$1:$A$13</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>tray_type</t>
-  </si>
-  <si>
-    <t>2 mL反应试管托盘(201000726) [1-24]</t>
-  </si>
-  <si>
-    <t>2 mL试管磁子托盘(201000711) [1-24]</t>
-  </si>
-  <si>
-    <t>反应密封盖托盘(201000712) [1-1]</t>
-  </si>
-  <si>
-    <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
-  </si>
-  <si>
-    <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
-  </si>
-  <si>
-    <t>50 μL Tip 头托盘(201000815) [1-96]</t>
-  </si>
-  <si>
-    <t>1 mL Tip 头托盘(201000731) [1-96]</t>
-  </si>
-  <si>
-    <t>5 mL Tip 头托盘(201000512) [1-24]</t>
-  </si>
-  <si>
-    <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
-  </si>
-  <si>
-    <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
-  </si>
-  <si>
-    <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
-  </si>
-  <si>
-    <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
-  </si>
-  <si>
-    <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
-  </si>
-  <si>
-    <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TB-2-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,21 +56,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,44 +417,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
+    <col width="23.1796875" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tray_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TB-1-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>闪滤瓶外瓶托盘(201000728)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>闪滤外瓶|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TB-2-1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30 mL粉桶托盘(201000600)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A1|2-氯-N-苯基-丙酰胺|700mg;B1|NNP-77|100mg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2-氯-N-苯基-丙酰胺|未知;NNP-77|未知</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TB-2-2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2 mL试管磁子托盘(201000711)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2mL反应管磁子|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TB-2-3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2 mL反应试管托盘(201000726)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2mL反应管|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TB-2-4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>反应密封盖托盘(201000712)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>反应盖板|耗材库</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="A2:A101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="B2:B101" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>tray_type_options</formula1>
     </dataValidation>
   </dataValidations>
@@ -468,77 +596,106 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>2 mL反应试管托盘(201000726) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2 mL试管磁子托盘(201000711) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>反应密封盖托盘(201000712) [1-1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>50 μL Tip 头托盘(201000815) [1-96]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1 mL Tip 头托盘(201000731) [1-96]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5 mL Tip 头托盘(201000512) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D7E3A9-74EA-4397-AFE3-7DE1D4207FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC42CBDA-891B-482C-8B19-1DBF506DF479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>position</t>
   </si>
@@ -35,31 +35,85 @@
     <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
   </si>
   <si>
-    <t>TB-2-1</t>
-  </si>
-  <si>
-    <t>2 mL试剂瓶托盘(201000730)</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>碘苯|1-2-3;1-2B;2,2,6,6-四甲基-3,5-庚二酮|2-3</t>
+    <t>TB-1-1</t>
+  </si>
+  <si>
+    <t>2 mL反应试管托盘(201000726)</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>2mL反应管|耗材库</t>
+  </si>
+  <si>
+    <t>TB-1-2</t>
+  </si>
+  <si>
+    <t>反应密封盖托盘(201000712)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>反应盖板|耗材库</t>
+  </si>
+  <si>
+    <t>TB-1-3</t>
+  </si>
+  <si>
+    <t>闪滤瓶内瓶托盘(201000727)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>闪滤内瓶|耗材库</t>
+  </si>
+  <si>
+    <t>TB-1-4</t>
+  </si>
+  <si>
+    <t>闪滤瓶外瓶托盘(201000728)</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>闪滤外瓶|耗材库</t>
   </si>
   <si>
     <t>TB-2-2</t>
   </si>
   <si>
-    <t>2 mL反应试管托盘(201000726)</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>40 mL试剂瓶托盘(201000503)</t>
   </si>
   <si>
     <t>3-2</t>
   </si>
   <si>
-    <t>2mL反应管|耗材库</t>
+    <t>炔醇酯-4Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-2F (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3F (溶液，0.1M in CH2Cl2）|未知</t>
+  </si>
+  <si>
+    <t>TB-2-4</t>
+  </si>
+  <si>
+    <t>2 mL试管磁子托盘(201000711)</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2mL反应管磁子|耗材库</t>
   </si>
   <si>
     <t>2 mL反应试管托盘(201000726) [1-24]</t>
@@ -101,7 +155,7 @@
     <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
   </si>
   <si>
-    <t>A1|碘苯|2mL;A2|2,2,6,6-四甲基-3,5-庚二酮|2mL</t>
+    <t>A1|炔醇酯-4Me (溶液，0.1M in CH2Cl2）|40mL;A2|炔醇酯-3Me (溶液，0.1M in CH2Cl2）|40mL;A3|炔醇酯-2F (溶液，0.1M in CH2Cl2）|40mL;B1|炔醇酯-3F (溶液，0.1M in CH2Cl2）|40mL;B2|炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|40mL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,8 +199,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -449,12 +506,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="38.7265625" customWidth="1"/>
-    <col min="3" max="3" width="59.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" customWidth="1"/>
+    <col min="3" max="3" width="80.26953125" customWidth="1"/>
     <col min="4" max="4" width="11.90625" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
   </cols>
@@ -478,43 +538,115 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="70" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="A2:A98" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showInputMessage="1" sqref="B2:B98" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>tray_type_options</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="77" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -525,67 +657,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC42CBDA-891B-482C-8B19-1DBF506DF479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BE68ED-EE8D-47A9-8C8D-AFE8DFBC4A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>position</t>
   </si>
@@ -35,127 +35,106 @@
     <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
   </si>
   <si>
+    <t>TB-2-1</t>
+  </si>
+  <si>
+    <t>2 mL试管磁子托盘(201000711)</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2mL反应管磁子|耗材库</t>
+  </si>
+  <si>
+    <t>TB-2-2</t>
+  </si>
+  <si>
+    <t>2 mL反应试管托盘(201000726)</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2mL反应管|耗材库</t>
+  </si>
+  <si>
+    <t>TB-2-3</t>
+  </si>
+  <si>
+    <t>反应密封盖托盘(201000712)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>反应盖板|耗材库</t>
+  </si>
+  <si>
+    <t>TB-2-4</t>
+  </si>
+  <si>
+    <t>闪滤瓶外瓶托盘(201000728)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>闪滤外瓶|耗材库</t>
+  </si>
+  <si>
+    <t>2 mL反应试管托盘(201000726) [1-24]</t>
+  </si>
+  <si>
+    <t>2 mL试管磁子托盘(201000711) [1-24]</t>
+  </si>
+  <si>
+    <t>反应密封盖托盘(201000712) [1-1]</t>
+  </si>
+  <si>
+    <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
+  </si>
+  <si>
+    <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
+  </si>
+  <si>
+    <t>50 μL Tip 头托盘(201000815) [1-96]</t>
+  </si>
+  <si>
+    <t>1 mL Tip 头托盘(201000731) [1-96]</t>
+  </si>
+  <si>
+    <t>5 mL Tip 头托盘(201000512) [1-24]</t>
+  </si>
+  <si>
+    <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
+  </si>
+  <si>
+    <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
+  </si>
+  <si>
+    <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
+  </si>
+  <si>
+    <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
+  </si>
+  <si>
+    <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
+  </si>
+  <si>
     <t>TB-1-1</t>
   </si>
   <si>
-    <t>2 mL反应试管托盘(201000726)</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>2-1</t>
-  </si>
-  <si>
-    <t>2mL反应管|耗材库</t>
-  </si>
-  <si>
-    <t>TB-1-2</t>
-  </si>
-  <si>
-    <t>反应密封盖托盘(201000712)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>反应盖板|耗材库</t>
-  </si>
-  <si>
-    <t>TB-1-3</t>
-  </si>
-  <si>
-    <t>闪滤瓶内瓶托盘(201000727)</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>闪滤内瓶|耗材库</t>
-  </si>
-  <si>
-    <t>TB-1-4</t>
-  </si>
-  <si>
-    <t>闪滤瓶外瓶托盘(201000728)</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>闪滤外瓶|耗材库</t>
-  </si>
-  <si>
-    <t>TB-2-2</t>
-  </si>
-  <si>
-    <t>40 mL试剂瓶托盘(201000503)</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>炔醇酯-4Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-2F (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3F (溶液，0.1M in CH2Cl2）|未知</t>
-  </si>
-  <si>
-    <t>TB-2-4</t>
-  </si>
-  <si>
-    <t>2 mL试管磁子托盘(201000711)</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>2mL反应管磁子|耗材库</t>
-  </si>
-  <si>
-    <t>2 mL反应试管托盘(201000726) [1-24]</t>
-  </si>
-  <si>
-    <t>2 mL试管磁子托盘(201000711) [1-24]</t>
-  </si>
-  <si>
-    <t>反应密封盖托盘(201000712) [1-1]</t>
-  </si>
-  <si>
-    <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
-  </si>
-  <si>
-    <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
-  </si>
-  <si>
-    <t>50 μL Tip 头托盘(201000815) [1-96]</t>
-  </si>
-  <si>
-    <t>1 mL Tip 头托盘(201000731) [1-96]</t>
-  </si>
-  <si>
-    <t>5 mL Tip 头托盘(201000512) [1-24]</t>
-  </si>
-  <si>
-    <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
-  </si>
-  <si>
-    <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
-  </si>
-  <si>
-    <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
-  </si>
-  <si>
-    <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
-  </si>
-  <si>
-    <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
-  </si>
-  <si>
-    <t>A1|炔醇酯-4Me (溶液，0.1M in CH2Cl2）|40mL;A2|炔醇酯-3Me (溶液，0.1M in CH2Cl2）|40mL;A3|炔醇酯-2F (溶液，0.1M in CH2Cl2）|40mL;B1|炔醇酯-3F (溶液，0.1M in CH2Cl2）|40mL;B2|炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|40mL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -199,10 +178,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,13 +489,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="1"/>
     <col min="2" max="2" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="80.26953125" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="1" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
   </cols>
   <sheetData>
@@ -540,7 +520,7 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
@@ -555,85 +535,62 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="70" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="1"/>
+      <c r="C6" s="2">
+        <v>96</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -657,67 +614,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -1,166 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BE68ED-EE8D-47A9-8C8D-AFE8DFBC4A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="batch_in_tray" sheetId="1" r:id="rId1"/>
-    <sheet name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_in_tray" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="tray_type_options">validation_meta!$A$1:$A$13</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>tray_type</t>
-  </si>
-  <si>
-    <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
-  </si>
-  <si>
-    <t>TB-2-1</t>
-  </si>
-  <si>
-    <t>2 mL试管磁子托盘(201000711)</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2mL反应管磁子|耗材库</t>
-  </si>
-  <si>
-    <t>TB-2-2</t>
-  </si>
-  <si>
-    <t>2 mL反应试管托盘(201000726)</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2mL反应管|耗材库</t>
-  </si>
-  <si>
-    <t>TB-2-3</t>
-  </si>
-  <si>
-    <t>反应密封盖托盘(201000712)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>反应盖板|耗材库</t>
-  </si>
-  <si>
-    <t>TB-2-4</t>
-  </si>
-  <si>
-    <t>闪滤瓶外瓶托盘(201000728)</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>闪滤外瓶|耗材库</t>
-  </si>
-  <si>
-    <t>2 mL反应试管托盘(201000726) [1-24]</t>
-  </si>
-  <si>
-    <t>2 mL试管磁子托盘(201000711) [1-24]</t>
-  </si>
-  <si>
-    <t>反应密封盖托盘(201000712) [1-1]</t>
-  </si>
-  <si>
-    <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
-  </si>
-  <si>
-    <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
-  </si>
-  <si>
-    <t>50 μL Tip 头托盘(201000815) [1-96]</t>
-  </si>
-  <si>
-    <t>1 mL Tip 头托盘(201000731) [1-96]</t>
-  </si>
-  <si>
-    <t>5 mL Tip 头托盘(201000512) [1-24]</t>
-  </si>
-  <si>
-    <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
-  </si>
-  <si>
-    <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
-  </si>
-  <si>
-    <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
-  </si>
-  <si>
-    <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
-  </si>
-  <si>
-    <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
-  </si>
-  <si>
-    <t>TB-1-1</t>
-  </si>
-  <si>
-    <t>2-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,25 +56,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -485,200 +421,369 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="30.6328125" customWidth="1"/>
-    <col min="3" max="3" width="80.26953125" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39" customWidth="1"/>
+    <col width="10.26953125" customWidth="1" min="1" max="1"/>
+    <col width="30.6328125" customWidth="1" min="2" max="2"/>
+    <col width="80.26953125" customWidth="1" min="3" max="3"/>
+    <col width="11.90625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2">
-        <v>96</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tray_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TB-1-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2 mL反应试管托盘(201000726)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2 mL反应管|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TB-1-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>反应密封盖托盘(201000712)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>反应密封盖|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TB-1-3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>闪滤瓶内瓶托盘(201000727)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>闪滤瓶内瓶|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TB-1-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>闪滤瓶外瓶托盘(201000728)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>闪滤瓶外瓶|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TB-2-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2 mL试剂瓶托盘(201000730)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A1|炔醇酯-4Me (溶液，0.1M in CH2Cl2）|2mL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>炔醇酯-4Me (溶液，0.1M in CH2Cl2）|未知</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TB-2-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>40 mL试剂瓶托盘(201000503)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A1|炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|15mL;A2|炔醇酯-3Me (溶液，0.1M in CH2Cl2）|9mL;A3|炔醇酯-2F (溶液，0.1M in CH2Cl2）|9mL;B1|炔醇酯-3F (溶液，0.1M in CH2Cl2）|12mL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-2F (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3F (溶液，0.1M in CH2Cl2）|未知</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TB-2-3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5 mL Tip 头托盘(201000512)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5 mL Tip头|耗材库</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TB-2-4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2 mL试管磁子托盘(201000711)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2 mL反应管磁子|耗材库</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="A2:A98" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="A2:A98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" sqref="B2:B98" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation sqref="B2:B98" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>tray_type_options</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="77" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="77" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>2 mL反应试管托盘(201000726) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2 mL试管磁子托盘(201000711) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>反应密封盖托盘(201000712) [1-1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>闪滤瓶内瓶托盘(201000727) [1-48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>闪滤瓶外瓶托盘(201000728) [1-48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>50 μL Tip 头托盘(201000815) [1-96]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1 mL Tip 头托盘(201000731) [1-96]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5 mL Tip 头托盘(201000512) [1-24]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30 mL粉桶托盘(201000600) [A1-B1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2 mL试剂瓶托盘(201000730) [A1-F8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8 mL试剂瓶托盘(201000502) [A1-C4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40 mL试剂瓶托盘(201000503) [A1-B3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.26953125" customWidth="1" min="1" max="1"/>
@@ -461,12 +461,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2 mL反应试管托盘(201000726)</t>
+          <t>闪滤瓶内瓶托盘(201000727)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2 mL反应管|耗材库</t>
+          <t>闪滤瓶内瓶|耗材库</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>反应密封盖托盘(201000712)</t>
+          <t>闪滤瓶外瓶托盘(201000728)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,169 +503,115 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>反应密封盖|耗材库</t>
+          <t>闪滤瓶外瓶|耗材库</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TB-1-3</t>
+          <t>TB-2-1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>闪滤瓶内瓶托盘(201000727)</t>
+          <t>1 mL Tip 头托盘(201000731)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>闪滤瓶内瓶|耗材库</t>
+          <t>1 mL Tip头|耗材库</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TB-1-4</t>
+          <t>TB-2-2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>闪滤瓶外瓶托盘(201000728)</t>
+          <t>2 mL试管磁子托盘(201000711)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>闪滤瓶外瓶|耗材库</t>
+          <t>2 mL反应管磁子|耗材库</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TB-2-1</t>
+          <t>TB-2-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2 mL试剂瓶托盘(201000730)</t>
+          <t>2 mL反应试管托盘(201000726)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A1|炔醇酯-4Me (溶液，0.1M in CH2Cl2）|2mL</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>炔醇酯-4Me (溶液，0.1M in CH2Cl2）|未知</t>
+          <t>2 mL反应管|耗材库</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TB-2-2</t>
+          <t>TB-2-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40 mL试剂瓶托盘(201000503)</t>
+          <t>反应密封盖托盘(201000712)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A1|炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|15mL;A2|炔醇酯-3Me (溶液，0.1M in CH2Cl2）|9mL;A3|炔醇酯-2F (溶液，0.1M in CH2Cl2）|9mL;B1|炔醇酯-3F (溶液，0.1M in CH2Cl2）|12mL</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>炔醇酯-4Ph (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3Me (溶液，0.1M in CH2Cl2）|未知;炔醇酯-2F (溶液，0.1M in CH2Cl2）|未知;炔醇酯-3F (溶液，0.1M in CH2Cl2）|未知</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TB-2-3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5 mL Tip 头托盘(201000512)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3-3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5 mL Tip头|耗材库</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TB-2-4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2 mL试管磁子托盘(201000711)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2 mL反应管磁子|耗材库</t>
+          <t>反应密封盖|耗材库</t>
         </is>
       </c>
     </row>
